--- a/inputs/slope/input_template_reliability6.xlsx
+++ b/inputs/slope/input_template_reliability6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/cursor_projects/xslope/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321DF72C-B89A-6D4E-A0E3-5DA21E77B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91B84CC-2267-7D4F-B58B-08456A43C610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32380" yWindow="1180" windowWidth="32580" windowHeight="22900" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="30500" yWindow="1260" windowWidth="32580" windowHeight="22900" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="140">
   <si>
     <t>X</t>
   </si>
@@ -577,6 +577,9 @@
   </si>
   <si>
     <t>Tres</t>
+  </si>
+  <si>
+    <t>soil</t>
   </si>
 </sst>
 </file>
@@ -995,7 +998,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6295,16 +6312,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6438,36 +6455,38 @@
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="3">
         <v>120</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>400</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>30</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>120</v>
       </c>
-      <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>8</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>100</v>
       </c>
-      <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -6925,71 +6944,71 @@
     <mergeCell ref="L19:Q19"/>
     <mergeCell ref="L2:Q2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:E4">
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>$D4="cp"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E5:F15">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$D5="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:G4">
-    <cfRule type="expression" dxfId="9" priority="4">
-      <formula>$D4="mc"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G5:H7 G8:J15">
-    <cfRule type="expression" dxfId="8" priority="13">
+    <cfRule type="expression" dxfId="10" priority="15">
       <formula>$D5="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:I4">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <conditionalFormatting sqref="I4">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>$D4="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:J7">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>$D5="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$D4="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:N15">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>$D4="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O15">
-    <cfRule type="expression" dxfId="3" priority="12">
+    <cfRule type="expression" dxfId="5" priority="14">
       <formula>$D4="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:Q7">
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>$D4="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:Q15">
-    <cfRule type="expression" dxfId="1" priority="9">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$D8="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:V15">
-    <cfRule type="expression" dxfId="0" priority="7">
+    <cfRule type="expression" dxfId="2" priority="9">
       <formula>$D4="cp"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F4">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$D4="cp"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:H4">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$D4="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D15 C4" xr:uid="{EE18A772-4B35-664E-B682-D915CEF97058}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D15" xr:uid="{EE18A772-4B35-664E-B682-D915CEF97058}">
       <formula1>$C$22:$C$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K15 J4" xr:uid="{829D28B8-D45C-5648-988B-473A68569983}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K15 J4" xr:uid="{829D28B8-D45C-5648-988B-473A68569983}">
       <formula1>$C$26:$C$28</formula1>
     </dataValidation>
   </dataValidations>
